--- a/temp/MACRO_VISA_20250604.xlsx
+++ b/temp/MACRO_VISA_20250604.xlsx
@@ -471,12 +471,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>10500</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10500,0</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -496,12 +498,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>789.45</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>789,45</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -521,12 +525,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>32199</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>32199,0</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -546,12 +552,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>264400</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>264400,0</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -571,12 +579,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>21274.69</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>21274,69</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -596,12 +606,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>5750</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5750,0</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
